--- a/Jacobs_etal_2018/Jacobs_etal_2018_Table3_snapshot.xlsx
+++ b/Jacobs_etal_2018/Jacobs_etal_2018_Table3_snapshot.xlsx
@@ -3497,13 +3497,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20A72C09-D161-408E-AED5-E1F3206CEC88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99BF32CC-C995-491D-9091-D65EEB68C536}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4E48A6B-2047-438F-9629-F1C79A3CBB2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC4B8590-5111-4A6D-B1CB-A1EC8C2E9DE0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71B00A3-CC40-4D1D-B71A-A83E557F321F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED275BDE-E321-4F31-B4D0-75779BBE83B6}"/>
 </file>
--- a/Jacobs_etal_2018/Jacobs_etal_2018_Table3_snapshot.xlsx
+++ b/Jacobs_etal_2018/Jacobs_etal_2018_Table3_snapshot.xlsx
@@ -3497,13 +3497,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99BF32CC-C995-491D-9091-D65EEB68C536}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97906256-8F29-49D5-BD4A-5026D5FED5DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC4B8590-5111-4A6D-B1CB-A1EC8C2E9DE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C169DA2-A499-46E0-A6F2-B2F90B0921BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED275BDE-E321-4F31-B4D0-75779BBE83B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71320C51-FC91-461A-8223-B30C33BCCC88}"/>
 </file>